--- a/MentorPodAttendance.xlsx
+++ b/MentorPodAttendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,30 +469,30 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>zola.aguilar@warriorlife.net</t>
+          <t>lila.granados@warriorlife.net</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aguilar</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Business Solutions Project (PMBS)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -505,22 +505,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>zola.aguilar@warriorlife.net</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Aguilar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -545,17 +545,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -656,31 +656,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -705,30 +705,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>kasper.kalani@warriorlife.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -741,17 +741,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -781,17 +781,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -884,35 +884,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -928,31 +932,31 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -960,7 +964,11 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -973,32 +981,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>tadeo.loureiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1017,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1053,17 +1057,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1076,7 +1080,11 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1089,17 +1097,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1120,31 +1128,31 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1160,31 +1168,31 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1200,31 +1208,31 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1249,32 +1257,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>hana.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Awareness Project (PMCA)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1293,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1312,7 +1316,11 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1325,17 +1333,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1356,31 +1364,31 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1388,30 +1396,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1432,26 +1444,26 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1466,37 +1478,37 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1504,7 +1516,11 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1517,57 +1533,53 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ingrid.zavala@warriorlife.net</t>
+          <t>sania.morales@warriorlife.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zavala</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1580,35 +1592,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>vidya.karimi@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Karimi</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1616,35 +1632,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>milena.moreau@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1652,30 +1672,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1688,35 +1712,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>ingrid.zavala@warriorlife.net</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Zavala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1724,7 +1752,11 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1737,53 +1769,53 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>solene.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1798,32 +1830,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>vidya.karimi@warriorlife.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Karimi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1838,32 +1870,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>milena.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1876,30 +1908,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1914,32 +1950,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1952,30 +1988,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1988,70 +2028,70 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>camila.obradovic@warriorlife.net</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2064,30 +2104,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2108,26 +2152,26 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2140,30 +2184,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2176,35 +2224,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2214,77 +2266,73 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>darius.paredes@warriorlife.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2292,35 +2340,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2328,35 +2380,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2364,35 +2420,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2408,31 +2468,31 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2448,31 +2508,31 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2488,71 +2548,67 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>hina.sepulveda@warriorlife.net</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2568,31 +2624,31 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2608,26 +2664,26 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2640,30 +2696,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2676,30 +2736,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2712,71 +2776,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>hazel.svensson@warriorlife.net</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2784,35 +2852,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2828,31 +2900,31 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2868,31 +2940,31 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2908,31 +2980,31 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2940,35 +3012,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2976,71 +3052,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>stellan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3048,35 +3128,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3086,37 +3170,37 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3126,37 +3210,37 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3164,35 +3248,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3202,73 +3290,73 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>hedda.ibarra@warriorlife.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3276,35 +3364,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3320,31 +3412,31 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3360,31 +3452,31 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3392,35 +3484,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3430,77 +3526,73 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>edda.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3516,31 +3608,31 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3548,35 +3640,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3584,35 +3680,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3628,31 +3728,31 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3662,37 +3762,37 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3700,75 +3800,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>naila.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3784,31 +3884,31 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3824,31 +3924,31 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3856,35 +3956,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3892,35 +3996,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3928,35 +4036,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3972,71 +4084,67 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>ulla.mariotti@warriorlife.net</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4052,31 +4160,31 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4084,35 +4192,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4128,31 +4240,31 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4160,35 +4272,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4204,67 +4320,67 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>remy.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4272,30 +4388,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>lorcan.milburn@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Lorcan</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4308,35 +4428,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4352,31 +4476,31 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>alec.sheridan@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Alec</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sheridan</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4384,35 +4508,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>lian.zoric@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zoric</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4420,75 +4548,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>ilana.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4504,31 +4632,31 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4536,35 +4664,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4572,35 +4704,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>rhys.mubarak@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4616,31 +4752,31 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4648,75 +4784,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>zara.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4724,35 +4860,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4762,37 +4902,37 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4800,35 +4940,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4838,37 +4982,37 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4876,75 +5020,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>ivan.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4960,31 +5104,31 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5000,31 +5144,31 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>lorcan.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Lorcan</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5040,31 +5184,31 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5080,31 +5224,31 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>alec.sheridan@warriorlife.net</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Alec</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Sheridan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5112,35 +5256,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>lian.zoric@warriorlife.net</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>Zoric</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5156,67 +5304,67 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>kavya.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5232,31 +5380,31 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5264,35 +5412,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5302,32 +5454,32 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5342,32 +5494,32 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>rhys.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5380,30 +5532,34 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5418,77 +5574,73 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>nova.stanek@warriorlife.net</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5496,35 +5648,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5532,35 +5688,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5576,31 +5736,31 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5608,35 +5768,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5644,35 +5808,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5682,73 +5850,73 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>paloma.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr"/>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5764,31 +5932,31 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5804,31 +5972,31 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>saanvi.nazari@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Saanvi</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Nazari</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5844,31 +6012,31 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>elias.riordan@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Riordan</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5884,31 +6052,31 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5924,71 +6092,67 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ashwin.trevino@warriorlife.net</t>
+          <t>astrid.kaufman@warriorlife.net</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Ashwin</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Trevino</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5996,35 +6160,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6040,31 +6208,31 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6072,35 +6240,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6108,35 +6280,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6152,31 +6328,31 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>yael.ruggiero@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6184,71 +6360,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>sk.alvarez@warriorlife.net</t>
+          <t>meilan.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6264,31 +6444,31 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>yara.gundersen@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Gundersen</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6298,37 +6478,37 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kenji.herrera@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Kenji</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6336,35 +6516,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>lyra.katayama@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Lyra</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Katayama</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6372,35 +6556,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ameer.bosco@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ameer</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>bosco</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6410,73 +6598,73 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>odlyscorin.almeida@warriorlife.net</t>
+          <t>danilo.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Odalys</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Almeida</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>r.fournier@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Selina</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Fournier</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6484,35 +6672,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>simone.leclerc@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Leclerc</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6520,35 +6712,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>amara.mbeki@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Amara</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6556,35 +6752,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>laila.pinheiro@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Laila</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Pinheiro</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6592,35 +6792,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>shiro.somerville@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Shiro</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6628,35 +6832,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>theo.sundaram@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sundaram</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6664,71 +6872,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>orla.devlin@warriorlife.net</t>
+          <t>zola.shaikh@warriorlife.net</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Orla</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Devlin</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>desmond.gascoigne@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Gascoigne</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6736,35 +6948,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>galina.ramaswamy@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ramaswamy</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6772,35 +6988,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>rune.sifuentes@warriorlife.net</t>
+          <t>saanvi.nazari@warriorlife.net</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>Saanvi</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Nazari</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6808,35 +7028,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>saoirse.sifuentes@warriorlife.net</t>
+          <t>elias.riordan@warriorlife.net</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Saoirse</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Riordan</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6844,35 +7068,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>sadie.sotelo@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Sadie</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6880,35 +7108,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>faris.valdez@warriorlife.net</t>
+          <t>ashwin.trevino@warriorlife.net</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Faris</t>
+          <t>Ashwin</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Valdez</t>
+          <t>Trevino</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6916,71 +7148,75 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>asher.hakim@warriorlife.net</t>
+          <t>e.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Asher</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>tadeo.hakim@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6988,35 +7224,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>salim.jarrah@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Salim</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7024,35 +7264,39 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>kasper.winterbourne@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Winterbourne</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7060,43 +7304,1275 @@
           <t>Compete</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
+        <v>27</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Diya Sifuentes</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>emeka.nascimento@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Emeka</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Nascimento</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>27</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Diya Sifuentes</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>eero.rothman@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Eero</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Rothman</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>27</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Diya Sifuentes</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>yael.ruggiero@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Yael</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ruggiero</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>28</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sadie.dahlberg@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>sadie</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>dahlberg</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>28</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sk.alvarez@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>28</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>chandra.fonseca@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Chandra</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>28</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>yara.gundersen@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Yara</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Gundersen</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>28</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>kenji.herrera@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Kenji</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Herrera</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>28</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>lyra.katayama@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Lyra</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Katayama</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>28</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>sadie dahlberg</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ameer.bosco@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ameer</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>bosco</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>29</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>annika.jensen@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Annika</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Jensen</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>29</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>odlyscorin.almeida@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Odalys</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Almeida</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>29</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>r.fournier@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Selina</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Fournier</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>29</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>simone.leclerc@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Simone</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Leclerc</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>29</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>amara.mbeki@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Amara</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Mbeki</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>29</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>laila.pinheiro@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Laila</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Pinheiro</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>29</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>shiro.somerville@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Shiro</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Somerville</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>29</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Annika Jensen</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>theo.sundaram@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Sundaram</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>30</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>tadeo.mercado@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tadeo</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Community Awareness Project (PMCA)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>30</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>orla.devlin@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Orla</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Devlin</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>30</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>desmond.gascoigne@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Desmond</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Gascoigne</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>30</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>galina.ramaswamy@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Galina</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Ramaswamy</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>30</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>rune.sifuentes@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Rune</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Sifuentes</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>30</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>saoirse.sifuentes@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Saoirse</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Sifuentes</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>30</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sadie.sotelo@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Sadie</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Sotelo</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>30</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Tadeo Mercado</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>faris.valdez@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Faris</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Valdez</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
         <v>31</v>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>siri zhelezny</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>siri.zhelezny@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>siri</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>zhelezny</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>31</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>siri zhelezny</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>asher.hakim@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Asher</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Hakim</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Business Solutions Project (PMBS)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>31</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>siri zhelezny</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>tadeo.hakim@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Tadeo</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Hakim</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Business Solutions Project (PMBS)</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>31</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>siri zhelezny</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>salim.jarrah@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Salim</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Jarrah</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>31</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>siri zhelezny</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>kasper.winterbourne@warriorlife.net</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Kasper</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Winterbourne</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Experienced</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>31</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>siri zhelezny</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
         <is>
           <t>livia.yildirim@warriorlife.net</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Livia</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>Yildirim</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Novice</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MentorPodAttendance.xlsx
+++ b/MentorPodAttendance.xlsx
@@ -464,27 +464,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lila.granados@warriorlife.net</t>
+          <t>edda.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -540,27 +540,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -620,22 +620,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -690,32 +690,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kasper.kalani@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -723,7 +723,11 @@
           <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -736,37 +740,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>remy.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -776,27 +776,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -816,27 +816,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -856,27 +856,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -896,27 +896,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -936,27 +936,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -976,27 +976,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tadeo.loureiro@warriorlife.net</t>
+          <t>solene.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1012,27 +1012,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1052,27 +1052,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1092,27 +1092,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1132,27 +1132,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1252,27 +1252,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>hana.milburn@warriorlife.net</t>
+          <t>camila.obradovic@warriorlife.net</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1328,22 +1328,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1368,22 +1368,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1448,22 +1448,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1488,22 +1488,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1528,27 +1528,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sania.morales@warriorlife.net</t>
+          <t>zara.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1564,27 +1564,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1604,22 +1604,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1764,27 +1764,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>solene.moreau@warriorlife.net</t>
+          <t>darius.paredes@warriorlife.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1840,27 +1840,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>vidya.karimi@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karimi</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1880,27 +1880,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>milena.moreau@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1920,27 +1920,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1960,27 +1960,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2000,27 +2000,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2040,27 +2040,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>camila.obradovic@warriorlife.net</t>
+          <t>zola.shaikh@warriorlife.net</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2076,27 +2076,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2116,27 +2116,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2156,27 +2156,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2196,27 +2196,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2236,27 +2236,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2276,27 +2276,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>darius.paredes@warriorlife.net</t>
+          <t>e.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2312,27 +2312,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2352,27 +2352,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2392,27 +2392,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2432,27 +2432,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2472,27 +2472,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2502,47 +2502,43 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>kavya.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2552,33 +2548,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hina.sepulveda@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2588,27 +2588,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2628,27 +2628,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2668,27 +2668,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2748,27 +2748,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2829,22 +2829,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2989,22 +2989,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3029,22 +3029,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3064,27 +3064,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>stellan.vargas@warriorlife.net</t>
+          <t>meilan.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3100,27 +3100,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>vidya.karimi@warriorlife.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Karimi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3140,27 +3140,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>milena.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3180,27 +3180,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3220,27 +3220,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3260,27 +3260,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3300,27 +3300,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>hedda.ibarra@warriorlife.net</t>
+          <t>lila.granados@warriorlife.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -3336,27 +3336,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3376,27 +3376,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3416,27 +3416,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3456,27 +3456,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3496,27 +3496,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3526,43 +3526,47 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>edda.krishnan@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3572,37 +3576,33 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>hedda.ibarra@warriorlife.net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3612,27 +3612,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3652,22 +3652,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3692,22 +3692,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3732,27 +3732,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3772,22 +3772,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3808,37 +3808,41 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>naila.krishnan@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3848,37 +3852,33 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>annika.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3888,27 +3888,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3928,27 +3928,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3968,27 +3968,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4008,27 +4008,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4048,27 +4048,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4088,27 +4088,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ulla.mariotti@warriorlife.net</t>
+          <t>tadeo.mercado@warriorlife.net</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -4124,27 +4124,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4164,27 +4164,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4204,27 +4204,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4244,27 +4244,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>rhys.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4284,27 +4284,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4324,17 +4324,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>remy.milburn@warriorlife.net</t>
+          <t>hana.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -4360,27 +4360,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4400,27 +4400,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4440,27 +4440,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4480,27 +4480,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4520,27 +4520,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4560,27 +4560,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ilana.palermo@warriorlife.net</t>
+          <t>danilo.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -4596,27 +4596,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4636,27 +4636,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4676,27 +4676,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4716,27 +4716,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4796,17 +4796,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>zara.palermo@warriorlife.net</t>
+          <t>ilana.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -4832,27 +4832,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4872,27 +4872,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4912,27 +4912,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4952,27 +4952,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4992,27 +4992,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5028,37 +5028,41 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ivan.sifuentes@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
+          <t>Independent Business Plan (EIB)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5068,37 +5072,33 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>hina.sepulveda@warriorlife.net</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5108,22 +5108,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5188,22 +5188,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5308,27 +5308,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>kavya.sotelo@warriorlife.net</t>
+          <t>ivan.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -5344,27 +5344,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5384,27 +5384,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5424,27 +5424,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5464,27 +5464,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5504,27 +5504,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>rhys.mubarak@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5540,38 +5540,34 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>nova.stanek@warriorlife.net</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -5589,28 +5585,32 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>nova.stanek@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5625,17 +5625,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5665,17 +5665,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5705,17 +5705,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5745,17 +5745,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5785,17 +5785,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5810,44 +5810,40 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>stellan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -5860,33 +5856,37 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>paloma.zabala@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5896,27 +5896,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5936,27 +5936,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5976,27 +5976,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6016,27 +6016,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6056,27 +6056,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6096,27 +6096,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>astrid.kaufman@warriorlife.net</t>
+          <t>sadie.dahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -6132,27 +6132,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6172,27 +6172,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6212,27 +6212,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6252,27 +6252,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6292,27 +6292,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6332,27 +6332,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6372,27 +6372,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>meilan.zabala@warriorlife.net</t>
+          <t>astrid.kaufman@warriorlife.net</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -6408,22 +6408,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6488,22 +6488,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6528,27 +6528,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6568,27 +6568,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6608,22 +6608,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>danilo.nuri@warriorlife.net</t>
+          <t>kasper.kalani@warriorlife.net</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6644,27 +6644,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6684,22 +6684,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>chandra.fonseca@warriorlife.net</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Chandra</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6724,27 +6724,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6764,27 +6764,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>saanvi.nazari@warriorlife.net</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>Saanvi</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Nazari</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6804,27 +6804,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>elias.riordan@warriorlife.net</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>Riordan</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6844,27 +6844,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6884,27 +6884,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>zola.shaikh@warriorlife.net</t>
+          <t>naila.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -6920,22 +6920,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6960,22 +6960,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7000,22 +7000,22 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>saanvi.nazari@warriorlife.net</t>
+          <t>emeka.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Saanvi</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Nazari</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7040,22 +7040,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>elias.riordan@warriorlife.net</t>
+          <t>eero.rothman@warriorlife.net</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Riordan</t>
+          <t>Rothman</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>yael.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7160,27 +7160,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>e.sifuentes@warriorlife.net</t>
+          <t>tadeo.loureiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
@@ -7196,27 +7196,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7236,27 +7236,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7276,27 +7276,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7316,27 +7316,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7356,27 +7356,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7396,27 +7396,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>yael.ruggiero@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7436,27 +7436,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>sadie.dahlberg@warriorlife.net</t>
+          <t>ulla.mariotti@warriorlife.net</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Ulla</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Mariotti</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7512,27 +7512,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Ulla Mariotti</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7712,22 +7712,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>annika.jensen@warriorlife.net</t>
+          <t>sania.morales@warriorlife.net</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Sania</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Morales</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Sania Morales</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8028,27 +8028,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>tadeo.mercado@warriorlife.net</t>
+          <t>paloma.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Paloma</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Paloma Zabala</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">

--- a/MentorPodAttendance.xlsx
+++ b/MentorPodAttendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,27 +464,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>edda.krishnan@warriorlife.net</t>
+          <t>lila.granados@warriorlife.net</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -500,27 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>zola.aguilar@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aguilar</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -540,27 +540,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -620,22 +620,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -700,27 +700,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,43 +730,47 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>remy.milburn@warriorlife.net</t>
+          <t>ingrid.zavala@warriorlife.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Zavala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Business Services Operations (BOR)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -776,22 +780,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>kasper.kalani@warriorlife.net</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -799,14 +803,10 @@
           <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -816,27 +816,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -856,27 +856,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -936,27 +936,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -972,67 +972,71 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>solene.moreau@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1042,7 +1046,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1052,37 +1056,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>hana.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Awareness Project (PMCA)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1092,27 +1092,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1132,27 +1132,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1248,34 +1248,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>camila.obradovic@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Business Services Operations (BOR)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -1284,26 +1288,26 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1328,37 +1332,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>solene.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1368,27 +1368,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>zola.aguilar@warriorlife.net</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Aguilar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1408,27 +1408,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>vidya.karimi@warriorlife.net</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Karimi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1488,27 +1488,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>milena.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1524,34 +1524,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>zara.palermo@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -1560,31 +1564,31 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1594,37 +1598,37 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1634,7 +1638,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1644,37 +1648,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>camila.obradovic@warriorlife.net</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1724,27 +1724,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ingrid.zavala@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zavala</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1760,67 +1760,71 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>darius.paredes@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1836,31 +1840,31 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1876,31 +1880,31 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1910,37 +1914,37 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1965,29 +1969,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>darius.paredes@warriorlife.net</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -2005,22 +2005,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2030,73 +2030,77 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>zola.shaikh@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2112,31 +2116,31 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2152,31 +2156,31 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2192,31 +2196,31 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2232,31 +2236,31 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2272,31 +2276,31 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>e.sifuentes@warriorlife.net</t>
+          <t>hina.sepulveda@warriorlife.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2308,26 +2312,26 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2342,32 +2346,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2382,32 +2386,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2428,26 +2432,26 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2462,32 +2466,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2502,40 +2506,44 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kavya.sotelo@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -2544,31 +2552,31 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2584,38 +2592,34 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>hazel.svensson@warriorlife.net</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -2624,31 +2628,31 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2664,31 +2668,31 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2704,31 +2708,31 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2744,31 +2748,31 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2784,7 +2788,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2793,34 +2797,38 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hazel.svensson@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Business Services Operations (BOR)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2829,22 +2837,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2860,7 +2868,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2869,22 +2877,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2900,66 +2908,62 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>stellan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2980,31 +2984,31 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3014,32 +3018,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3060,34 +3064,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>meilan.zabala@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -3096,31 +3104,31 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>vidya.karimi@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karimi</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3130,37 +3138,37 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>milena.moreau@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3176,31 +3184,31 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3216,71 +3224,67 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>hedda.ibarra@warriorlife.net</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3290,73 +3294,77 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>lila.granados@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3372,31 +3380,31 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3412,31 +3420,31 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>rhys.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3452,31 +3460,31 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3492,66 +3500,62 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>edda.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3572,62 +3576,66 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>hedda.ibarra@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3648,26 +3656,26 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3688,26 +3696,26 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3728,31 +3736,31 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3762,32 +3770,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3808,107 +3816,107 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>naila.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>annika.jensen@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3924,31 +3932,31 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3964,31 +3972,31 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4004,31 +4012,31 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4038,37 +4046,37 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Naila Krishnan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4084,31 +4092,31 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>tadeo.mercado@warriorlife.net</t>
+          <t>remy.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -4120,31 +4128,31 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4154,37 +4162,37 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4194,37 +4202,37 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4234,37 +4242,37 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>rhys.mubarak@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4274,37 +4282,37 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4314,73 +4322,77 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>hana.milburn@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4396,38 +4408,34 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>ilana.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -4436,31 +4444,31 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4476,31 +4484,31 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4516,31 +4524,31 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4550,27 +4558,27 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>danilo.nuri@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4580,43 +4588,47 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+          <t>Independent Business Plan (EIB)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4632,31 +4644,31 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4672,31 +4684,31 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4712,26 +4724,26 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>zara.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4739,44 +4751,40 @@
           <t>Innovation Plan (EIP)</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4786,40 +4794,44 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ilana.palermo@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -4828,31 +4840,31 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4868,31 +4880,31 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4902,37 +4914,37 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4948,31 +4960,31 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4982,37 +4994,37 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5028,102 +5040,102 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>ivan.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>hina.sepulveda@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
+          <t>Independent Business Plan (EIB)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5144,11 +5156,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5184,26 +5196,26 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5218,17 +5230,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5264,11 +5276,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5304,31 +5316,31 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ivan.sifuentes@warriorlife.net</t>
+          <t>kavya.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -5340,31 +5352,31 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5374,37 +5386,37 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5414,37 +5426,37 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5460,31 +5472,31 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5500,31 +5512,31 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5534,40 +5546,44 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>nova.stanek@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -5576,7 +5592,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -5585,38 +5601,34 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>nova.stanek@warriorlife.net</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5625,17 +5637,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5656,7 +5668,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -5665,17 +5677,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5696,7 +5708,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -5705,17 +5717,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5736,7 +5748,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -5745,17 +5757,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5776,7 +5788,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5785,17 +5797,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5816,62 +5828,66 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>stellan.vargas@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5886,72 +5902,68 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>astrid.kaufman@warriorlife.net</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5966,32 +5978,32 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6012,26 +6024,26 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6046,32 +6058,32 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6092,67 +6104,71 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sadie.dahlberg@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6168,71 +6184,67 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>meilan.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6248,31 +6260,31 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6282,37 +6294,37 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6322,37 +6334,37 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6368,34 +6380,38 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>astrid.kaufman@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -6404,26 +6420,26 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6438,77 +6454,73 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>danilo.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6524,31 +6536,31 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6564,31 +6576,31 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6598,73 +6610,77 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>kasper.kalani@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6680,26 +6696,26 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6720,66 +6736,62 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>zola.shaikh@warriorlife.net</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>saanvi.nazari@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Saanvi</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Nazari</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6800,26 +6812,26 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>elias.riordan@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Riordan</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6840,26 +6852,26 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>saanvi.nazari@warriorlife.net</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Saanvi</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Nazari</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6880,62 +6892,66 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>naila.krishnan@warriorlife.net</t>
+          <t>elias.riordan@warriorlife.net</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Riordan</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6956,26 +6972,26 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>ashwin.trevino@warriorlife.net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Ashwin</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Trevino</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6990,32 +7006,32 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>e.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7023,44 +7039,40 @@
           <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7070,32 +7082,32 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>yael.ruggiero@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7110,32 +7122,32 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ashwin.trevino@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Ashwin</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Trevino</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7150,73 +7162,77 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>tadeo.loureiro@warriorlife.net</t>
+          <t>emeka.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>eero.rothman@warriorlife.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Rothman</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7232,31 +7248,31 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>yael.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7266,77 +7282,73 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>sadie.dahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>sk.alvarez@warriorlife.net</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Alvarez</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7352,26 +7364,26 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>chandra.fonseca@warriorlife.net</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Chandra</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7392,31 +7404,31 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>yara.gundersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Gundersen</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7432,34 +7444,38 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ulla.mariotti@warriorlife.net</t>
+          <t>kenji.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ulla</t>
+          <t>Kenji</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mariotti</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -7468,26 +7484,26 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>sk.alvarez@warriorlife.net</t>
+          <t>lyra.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Lyra</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>Katayama</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7502,37 +7518,37 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>ameer.bosco@warriorlife.net</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>ameer</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>bosco</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7542,77 +7558,73 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>yara.gundersen@warriorlife.net</t>
+          <t>annika.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Gundersen</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>kenji.herrera@warriorlife.net</t>
+          <t>odlyscorin.almeida@warriorlife.net</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Kenji</t>
+          <t>Odalys</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Almeida</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Professional Selling (PSE)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7622,37 +7634,37 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>lyra.katayama@warriorlife.net</t>
+          <t>r.fournier@warriorlife.net</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Lyra</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Katayama</t>
+          <t>Fournier</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Professional Selling (PSE)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7668,31 +7680,31 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ulla Mariotti</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ameer.bosco@warriorlife.net</t>
+          <t>simone.leclerc@warriorlife.net</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ameer</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>bosco</t>
+          <t>Leclerc</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Professional Selling (PSE)</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7702,68 +7714,72 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>sania.morales@warriorlife.net</t>
+          <t>amara.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Sania</t>
+          <t>Amara</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Morales</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr"/>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>odlyscorin.almeida@warriorlife.net</t>
+          <t>laila.pinheiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Odalys</t>
+          <t>Laila</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Almeida</t>
+          <t>Pinheiro</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7784,26 +7800,26 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>r.fournier@warriorlife.net</t>
+          <t>shiro.somerville@warriorlife.net</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Selina</t>
+          <t>Shiro</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fournier</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7818,32 +7834,32 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>simone.leclerc@warriorlife.net</t>
+          <t>theo.sundaram@warriorlife.net</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Leclerc</t>
+          <t>Sundaram</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7864,71 +7880,67 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>amara.mbeki@warriorlife.net</t>
+          <t>tadeo.mercado@warriorlife.net</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Amara</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Awareness Project (PMCA)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>laila.pinheiro@warriorlife.net</t>
+          <t>orla.devlin@warriorlife.net</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Laila</t>
+          <t>Orla</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Pinheiro</t>
+          <t>Devlin</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7944,31 +7956,31 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>shiro.somerville@warriorlife.net</t>
+          <t>desmond.gascoigne@warriorlife.net</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Shiro</t>
+          <t>Desmond</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Gascoigne</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7984,31 +7996,31 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sania Morales</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>theo.sundaram@warriorlife.net</t>
+          <t>galina.ramaswamy@warriorlife.net</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Galina</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sundaram</t>
+          <t>Ramaswamy</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -8018,40 +8030,44 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>paloma.zabala@warriorlife.net</t>
+          <t>rune.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Paloma</t>
+          <t>Rune</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr"/>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H194" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -8060,31 +8076,31 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>orla.devlin@warriorlife.net</t>
+          <t>saoirse.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Orla</t>
+          <t>Saoirse</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Devlin</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8094,32 +8110,32 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>desmond.gascoigne@warriorlife.net</t>
+          <t>sadie.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>Sadie</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gascoigne</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8134,37 +8150,37 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>galina.ramaswamy@warriorlife.net</t>
+          <t>faris.valdez@warriorlife.net</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Faris</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Ramaswamy</t>
+          <t>Valdez</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8174,44 +8190,40 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>rune.sifuentes@warriorlife.net</t>
+          <t>tadeo.loureiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -8220,31 +8232,31 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>saoirse.sifuentes@warriorlife.net</t>
+          <t>asher.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Saoirse</t>
+          <t>Asher</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8254,37 +8266,37 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>sadie.sotelo@warriorlife.net</t>
+          <t>tadeo.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Sadie</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8294,37 +8306,37 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Paloma Zabala</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>faris.valdez@warriorlife.net</t>
+          <t>salim.jarrah@warriorlife.net</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Faris</t>
+          <t>Salim</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Valdez</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8334,40 +8346,44 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>siri.zhelezny@warriorlife.net</t>
+          <t>kasper.winterbourne@warriorlife.net</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>siri</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>zhelezny</t>
+          <t>Winterbourne</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr"/>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -8376,26 +8392,26 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>asher.hakim@warriorlife.net</t>
+          <t>livia.yildirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Asher</t>
+          <t>Livia</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Yildirim</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8409,166 +8425,6 @@
         </is>
       </c>
       <c r="H203" t="inlineStr">
-        <is>
-          <t>Novice</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>31</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>siri zhelezny</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>tadeo.hakim@warriorlife.net</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Tadeo</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Hakim</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Business Solutions Project (PMBS)</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Novice</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>31</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>siri zhelezny</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>salim.jarrah@warriorlife.net</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Salim</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Jarrah</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Novice</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>31</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>siri zhelezny</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>kasper.winterbourne@warriorlife.net</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Kasper</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Winterbourne</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Experienced</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>31</v>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>siri zhelezny</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>livia.yildirim@warriorlife.net</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Livia</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Yildirim</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Business Solutions Project (PMBS)</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
         <is>
           <t>Novice</t>
         </is>

--- a/MentorPodAttendance.xlsx
+++ b/MentorPodAttendance.xlsx
@@ -464,27 +464,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lila.granados@warriorlife.net</t>
+          <t>hedda.ibarra@warriorlife.net</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Hedda</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -500,27 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -540,27 +540,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,27 +620,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -700,27 +700,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>Hedda Ibarra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ingrid.zavala@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zavala</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -780,27 +780,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kasper.kalani@warriorlife.net</t>
+          <t>hana.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalani</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -816,27 +816,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>zola.aguilar@warriorlife.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>Aguilar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -856,27 +856,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -896,27 +896,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -936,27 +936,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -976,27 +976,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1016,27 +1016,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kasper Kalani</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hana.milburn@warriorlife.net</t>
+          <t>remy.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1092,22 +1092,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1132,22 +1132,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1252,22 +1252,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1292,22 +1292,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hana Milburn</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>solene.moreau@warriorlife.net</t>
+          <t>danilo.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1368,22 +1368,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>zola.aguilar@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aguilar</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1528,22 +1528,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1568,22 +1568,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1608,22 +1608,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1648,27 +1648,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>camila.obradovic@warriorlife.net</t>
+          <t>zara.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1764,27 +1764,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1804,27 +1804,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1844,27 +1844,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1924,27 +1924,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>ingrid.zavala@warriorlife.net</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Zavala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1964,27 +1964,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>darius.paredes@warriorlife.net</t>
+          <t>ivan.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2000,27 +2000,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2040,27 +2040,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2080,27 +2080,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2120,27 +2120,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2160,27 +2160,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2200,27 +2200,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2240,27 +2240,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hina.sepulveda@warriorlife.net</t>
+          <t>kavya.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2316,27 +2316,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2356,27 +2356,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2396,27 +2396,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2436,27 +2436,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2516,27 +2516,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2546,32 +2546,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>stellan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2579,14 +2579,10 @@
           <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2596,33 +2592,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>hazel.svensson@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2632,27 +2632,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2712,27 +2712,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2752,27 +2752,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2792,27 +2792,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2832,27 +2832,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2868,41 +2868,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>sadie.dahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2912,33 +2908,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>stellan.vargas@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2948,27 +2948,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2988,27 +2988,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3028,27 +3028,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3068,27 +3068,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3108,27 +3108,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>kasper.winterbourne@warriorlife.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Winterbourne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3148,27 +3148,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3184,38 +3184,34 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>lila.granados@warriorlife.net</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Business Solutions Project (PMBS)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -3228,33 +3224,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>hedda.ibarra@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Hedda</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3264,27 +3264,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3304,27 +3304,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3344,27 +3344,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3384,27 +3384,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3424,27 +3424,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>rhys.mubarak@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3464,27 +3464,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hedda Ibarra</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>livia.yildirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Livia</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Yildirim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3504,27 +3504,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>edda.krishnan@warriorlife.net</t>
+          <t>annika.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -3540,22 +3540,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3580,22 +3580,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3620,22 +3620,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3660,27 +3660,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3700,22 +3700,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3740,27 +3740,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3770,13 +3770,13 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3785,32 +3785,28 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>edda.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3820,33 +3816,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>naila.krishnan@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3856,27 +3856,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3896,27 +3896,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3976,27 +3976,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4016,27 +4016,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4056,27 +4056,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Naila Krishnan</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4096,27 +4096,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>remy.milburn@warriorlife.net</t>
+          <t>tadeo.mercado@warriorlife.net</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Community Awareness Project (PMCA)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -4132,27 +4132,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4172,27 +4172,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4212,27 +4212,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4252,22 +4252,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4292,27 +4292,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4332,27 +4332,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4368,41 +4368,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>solene.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4412,33 +4408,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ilana.palermo@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4448,27 +4448,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4488,27 +4488,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4528,27 +4528,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4568,27 +4568,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4608,27 +4608,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>rhys.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4648,27 +4648,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4678,47 +4678,43 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>camila.obradovic@warriorlife.net</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4728,30 +4724,34 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>zara.palermo@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -4764,27 +4764,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4804,27 +4804,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4844,27 +4844,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4884,27 +4884,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4924,27 +4924,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4964,27 +4964,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5000,41 +5000,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>darius.paredes@warriorlife.net</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5044,33 +5040,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ivan.sifuentes@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5080,27 +5080,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5120,27 +5120,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>lorcan.milburn@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Lorcan</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5200,27 +5200,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5240,27 +5240,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>alec.sheridan@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Alec</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sheridan</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5280,27 +5280,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>lian.zoric@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zoric</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5320,27 +5320,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>kavya.sotelo@warriorlife.net</t>
+          <t>hina.sepulveda@warriorlife.net</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -5356,27 +5356,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5396,27 +5396,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>lorcan.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Lorcan</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5436,27 +5436,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>alec.sheridan@warriorlife.net</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Alec</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Sheridan</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5516,27 +5516,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5556,27 +5556,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>lian.zoric@warriorlife.net</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Zoric</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5637,22 +5637,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5677,22 +5677,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5717,22 +5717,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5757,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5797,22 +5797,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5837,22 +5837,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5877,22 +5877,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5953,17 +5953,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5993,17 +5993,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6033,17 +6033,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6073,17 +6073,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6113,17 +6113,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6153,17 +6153,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6184,26 +6184,26 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>meilan.zabala@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6211,7 +6211,11 @@
           <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -6229,32 +6233,28 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>meilan.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6389,22 +6389,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6429,22 +6429,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6454,43 +6454,47 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>danilo.nuri@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6500,37 +6504,33 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>tadeo.loureiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6540,27 +6540,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>sk.alvarez@warriorlife.net</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Alvarez</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6580,27 +6580,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6620,27 +6620,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>kenji.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>Kenji</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6660,27 +6660,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>salim.jarrah@warriorlife.net</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Salim</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6700,27 +6700,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>lyra.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Lyra</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Katayama</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6730,43 +6730,47 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>zola.shaikh@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Shaikh</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6776,37 +6780,33 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>ilana.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6816,27 +6816,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6856,27 +6856,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>saanvi.nazari@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Saanvi</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Nazari</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6896,27 +6896,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>elias.riordan@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Riordan</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6936,27 +6936,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6976,27 +6976,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Zola Shaikh</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ashwin.trevino@warriorlife.net</t>
+          <t>chandra.fonseca@warriorlife.net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Ashwin</t>
+          <t>Chandra</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Trevino</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7012,67 +7012,71 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>e.sifuentes@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7082,7 +7086,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7092,37 +7096,33 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>hazel.svensson@warriorlife.net</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7132,22 +7132,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7172,22 +7172,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>emeka.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7252,22 +7252,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Diya Sifuentes</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>yael.ruggiero@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7282,73 +7282,77 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>sadie.dahlberg@warriorlife.net</t>
+          <t>eero.rothman@warriorlife.net</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Rothman</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>sk.alvarez@warriorlife.net</t>
+          <t>ashwin.trevino@warriorlife.net</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Ashwin</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>Trevino</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7368,37 +7372,33 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>siri.zhelezny@warriorlife.net</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>siri</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>zhelezny</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7408,22 +7408,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>yara.gundersen@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gundersen</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7448,27 +7448,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>kenji.herrera@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Kenji</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7488,27 +7488,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>lyra.katayama@warriorlife.net</t>
+          <t>yara.gundersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Lyra</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Katayama</t>
+          <t>Gundersen</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7528,22 +7528,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ameer.bosco@warriorlife.net</t>
+          <t>saanvi.nazari@warriorlife.net</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ameer</t>
+          <t>Saanvi</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>bosco</t>
+          <t>Nazari</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7564,67 +7564,71 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>annika.jensen@warriorlife.net</t>
+          <t>elias.riordan@warriorlife.net</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Riordan</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>odlyscorin.almeida@warriorlife.net</t>
+          <t>yael.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Odalys</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Almeida</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7634,37 +7638,37 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>siri zhelezny</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>r.fournier@warriorlife.net</t>
+          <t>ameer.bosco@warriorlife.net</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Selina</t>
+          <t>ameer</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fournier</t>
+          <t>bosco</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7674,7 +7678,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7684,34 +7688,30 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>simone.leclerc@warriorlife.net</t>
+          <t>zola.shaikh@warriorlife.net</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Simone</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Leclerc</t>
+          <t>Shaikh</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -7724,27 +7724,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>amara.mbeki@warriorlife.net</t>
+          <t>odlyscorin.almeida@warriorlife.net</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Amara</t>
+          <t>Odalys</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Almeida</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Professional Selling (PSE)</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7764,22 +7764,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>laila.pinheiro@warriorlife.net</t>
+          <t>r.fournier@warriorlife.net</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Laila</t>
+          <t>Selina</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Pinheiro</t>
+          <t>Fournier</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7804,22 +7804,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>shiro.somerville@warriorlife.net</t>
+          <t>simone.leclerc@warriorlife.net</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Shiro</t>
+          <t>Simone</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Leclerc</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7844,27 +7844,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>theo.sundaram@warriorlife.net</t>
+          <t>amara.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Amara</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sundaram</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Professional Selling (PSE)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7874,73 +7874,77 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>tadeo.mercado@warriorlife.net</t>
+          <t>laila.pinheiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Laila</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Pinheiro</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr"/>
+          <t>Professional Selling (PSE)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>orla.devlin@warriorlife.net</t>
+          <t>shiro.somerville@warriorlife.net</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Orla</t>
+          <t>Shiro</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Devlin</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Professional Selling (PSE)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7956,31 +7960,31 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Zola Shaikh</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>desmond.gascoigne@warriorlife.net</t>
+          <t>theo.sundaram@warriorlife.net</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Desmond</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Gascoigne</t>
+          <t>Sundaram</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+          <t>Professional Selling (PSE)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7990,7 +7994,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -8000,37 +8004,33 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>galina.ramaswamy@warriorlife.net</t>
+          <t>e.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ramaswamy</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -8040,22 +8040,22 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>rune.sifuentes@warriorlife.net</t>
+          <t>orla.devlin@warriorlife.net</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>Orla</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Devlin</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -8080,27 +8080,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>saoirse.sifuentes@warriorlife.net</t>
+          <t>desmond.gascoigne@warriorlife.net</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Saoirse</t>
+          <t>Desmond</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Gascoigne</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -8120,22 +8120,22 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>sadie.sotelo@warriorlife.net</t>
+          <t>galina.ramaswamy@warriorlife.net</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Sadie</t>
+          <t>Galina</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Ramaswamy</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -8160,27 +8160,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>faris.valdez@warriorlife.net</t>
+          <t>rune.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Faris</t>
+          <t>Rune</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Valdez</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -8196,34 +8196,38 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>tadeo.loureiro@warriorlife.net</t>
+          <t>saoirse.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Saoirse</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr"/>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H198" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -8232,31 +8236,31 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>asher.hakim@warriorlife.net</t>
+          <t>sadie.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Asher</t>
+          <t>Sadie</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -8266,37 +8270,37 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Diya Sifuentes</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>tadeo.hakim@warriorlife.net</t>
+          <t>faris.valdez@warriorlife.net</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Faris</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Valdez</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Financial Consulting (FCE)</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -8306,7 +8310,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -8316,37 +8320,33 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>salim.jarrah@warriorlife.net</t>
+          <t>kasper.kalani@warriorlife.net</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Salim</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Kalani</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -8356,27 +8356,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>kasper.winterbourne@warriorlife.net</t>
+          <t>asher.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Asher</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Winterbourne</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -8396,22 +8396,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Kasper Kalani</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>livia.yildirim@warriorlife.net</t>
+          <t>tadeo.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Livia</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Yildirim</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">

--- a/MentorPodAttendance.xlsx
+++ b/MentorPodAttendance.xlsx
@@ -505,22 +505,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>priya.balakrishnan@warriorlife.net</t>
+          <t>lian.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Balakrishnan</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -545,22 +545,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hugo.farooqi@warriorlife.net</t>
+          <t>jian.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hugo</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Farooqi</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -585,22 +585,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pavel.maldonado@warriorlife.net</t>
+          <t>angelo.khatri@warriorlife.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Angelo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Khatri</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,22 +625,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bao.pereira@warriorlife.net</t>
+          <t>sirid.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Sigrid Clara (Noor)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -665,22 +665,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phoebe.sandoval@warriorlife.net</t>
+          <t>florian.rautio@warriorlife.net</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Florian</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sandoval</t>
+          <t>Rautio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -705,22 +705,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>naila.solberg@warriorlife.net</t>
+          <t>fiona.silveira@warriorlife.net</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Solberg</t>
+          <t>Silveira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -745,22 +745,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zola.ugarte@warriorlife.net</t>
+          <t>ingrid.zavala@warriorlife.net</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Ingrid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ugarte</t>
+          <t>Zavala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -821,22 +821,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zola.aguilar@warriorlife.net</t>
+          <t>gia.ferraro@warriorlife.net</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Gia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aguilar</t>
+          <t>Ferraro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>xanthe.delacroix@warriorlife.net</t>
+          <t>marco.greenway@warriorlife.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Xanthe</t>
+          <t>Marco</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Greenway</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>javier.jarvis@warriorlife.net</t>
+          <t>gabriel.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jarvis</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>freya.kowalczyk@warriorlife.net</t>
+          <t>mona.montague@warriorlife.net</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Freya</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Montague</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -981,22 +981,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>zoa.marchetti@warriorlife.net</t>
+          <t>ainsley.pandit@warriorlife.net</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Teodora</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marchetti</t>
+          <t>Pandit</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>magnus.sibanda@warriorlife.net</t>
+          <t>noor.renard@warriorlife.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Magnus</t>
+          <t>Noor</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sibanda</t>
+          <t>Renard</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1052,37 +1052,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Remy Milburn</t>
+          <t>Hana Milburn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>remy.milburn@warriorlife.net</t>
+          <t>klara.serrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Klara</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Serrano</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1101,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cyrus.dalmau@warriorlife.net</t>
+          <t>remy.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalmau</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mariam.mahmood@warriorlife.net</t>
+          <t>priya.balakrishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mahmood</t>
+          <t>Balakrishnan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1177,22 +1177,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nasir.moreau@warriorlife.net</t>
+          <t>hugo.farooqi@warriorlife.net</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Hugo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Farooqi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sinead.odhiambo@warriorlife.net</t>
+          <t>pavel.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sinead</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odhiambo</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1257,22 +1257,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mirra.ravindran@warriorlife.net</t>
+          <t>bao.pereira@warriorlife.net</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ravindran</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>vivienne.zambrano@warriorlife.net</t>
+          <t>phoebe.sandoval@warriorlife.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zambrano</t>
+          <t>Sandoval</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1328,26 +1328,26 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>danilo.nuri@warriorlife.net</t>
+          <t>naila.solberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Solberg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1355,7 +1355,11 @@
           <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -1364,26 +1368,26 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Danilo Nuri</t>
+          <t>Remy Milburn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>isla.baptiste@warriorlife.net</t>
+          <t>zola.ugarte@warriorlife.net</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Ugarte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1398,7 +1402,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1417,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ravi.jensen@warriorlife.net</t>
+          <t>danilo.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Danilo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1431,14 +1435,10 @@
           <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>vidya.karimi@warriorlife.net</t>
+          <t>isla.baptiste@warriorlife.net</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Vidya</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karimi</t>
+          <t>Baptiste</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1493,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>milena.moreau@warriorlife.net</t>
+          <t>ravi.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Milena</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1533,17 +1533,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gita.ponce@warriorlife.net</t>
+          <t>vidya.karimi@warriorlife.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gita</t>
+          <t>Vidya</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ponce</t>
+          <t>Karimi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1573,17 +1573,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kalina.sifuentes@warriorlife.net</t>
+          <t>milena.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kalina</t>
+          <t>Milena</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gita.zabala@warriorlife.net</t>
+          <t>gita.ponce@warriorlife.net</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Ponce</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1638,73 +1638,77 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>zara.palermo@warriorlife.net</t>
+          <t>kalina.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Kalina</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zara Palermo</t>
+          <t>Danilo Nuri</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>lian.callahan@warriorlife.net</t>
+          <t>gita.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Gita</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1729,32 +1733,28 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jian.jensen@warriorlife.net</t>
+          <t>zara.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1769,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>angelo.khatri@warriorlife.net</t>
+          <t>zola.aguilar@warriorlife.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Angelo</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Khatri</t>
+          <t>Aguilar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1809,22 +1809,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sirid.krishnan@warriorlife.net</t>
+          <t>xanthe.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sigrid Clara (Noor)</t>
+          <t>Xanthe</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -1849,22 +1849,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>florian.rautio@warriorlife.net</t>
+          <t>javier.jarvis@warriorlife.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Florian</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rautio</t>
+          <t>Jarvis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1889,22 +1889,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fiona.silveira@warriorlife.net</t>
+          <t>freya.kowalczyk@warriorlife.net</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Freya</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Silveira</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ingrid.zavala@warriorlife.net</t>
+          <t>zoa.marchetti@warriorlife.net</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ingrid</t>
+          <t>Teodora</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zavala</t>
+          <t>Marchetti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1960,37 +1960,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Zara Palermo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ivan.sifuentes@warriorlife.net</t>
+          <t>magnus.sibanda@warriorlife.net</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Magnus</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Sibanda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Sports &amp; Entertainment Marketing Operations (SEOR)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2000,37 +2004,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>arjun.duran@warriorlife.net</t>
+          <t>hina.sepulveda@warriorlife.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Hina</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Duran</t>
+          <t>Sepulveda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>zola.giordano@warriorlife.net</t>
+          <t>arjun.duran@warriorlife.net</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Zola</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Giordano</t>
+          <t>Duran</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2080,22 +2080,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>hadley.hakim@warriorlife.net</t>
+          <t>zola.giordano@warriorlife.net</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hadley</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hakim</t>
+          <t>Giordano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2120,22 +2120,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>yasmin.ingersoll@warriorlife.net</t>
+          <t>devika.olivares@warriorlife.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Devika</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ingersoll</t>
+          <t>Olivares</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2160,27 +2160,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ahana.vargas@warriorlife.net</t>
+          <t>theo.sathe@warriorlife.net</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ahana</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Sathe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2200,27 +2200,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>shalini.wickham@warriorlife.net</t>
+          <t>peeira.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Shalini</t>
+          <t>Quinn</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wickham</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2240,27 +2240,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ivan Sifuentes</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ravi.nkemdirim@warriorlife.net</t>
+          <t>ct.souza@warriorlife.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ravi</t>
+          <t>Vance Avani</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>nkemdirim</t>
+          <t>Souza</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2276,37 +2276,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Hina Sepulveda</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kavya.sotelo@warriorlife.net</t>
+          <t>t.zeidler@warriorlife.net</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Zeidler</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Financial Consulting (FCE)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2316,37 +2320,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>beatriz.krishnan@warriorlife.net</t>
+          <t>ivan.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2356,27 +2356,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>gabriel.mikkelsen@warriorlife.net</t>
+          <t>hadley.hakim@warriorlife.net</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Hadley</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Hakim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2396,27 +2396,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>noor.renard@warriorlife.net</t>
+          <t>yasmin.ingersoll@warriorlife.net</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Noor</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Renard</t>
+          <t>Ingersoll</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2436,22 +2436,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>soren.rosales@warriorlife.net</t>
+          <t>beatriz.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rosales</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>declan.sotelo@warriorlife.net</t>
+          <t>ahana.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Ahana</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sotelo</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Business Services Operations (BOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2516,22 +2516,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kavya Sotelo</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kavya.wahlberg@warriorlife.net</t>
+          <t>declan.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wahlberg</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2546,32 +2546,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>stellan.vargas@warriorlife.net</t>
+          <t>shalini.wickham@warriorlife.net</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Stellan</t>
+          <t>Shalini</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Wickham</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2579,7 +2579,11 @@
           <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -2588,31 +2592,31 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Ivan Sifuentes</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>neel.falconer@warriorlife.net</t>
+          <t>ravi.nkemdirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>ravi</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Falconer</t>
+          <t>nkemdirim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2632,37 +2636,33 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gia.ferraro@warriorlife.net</t>
+          <t>kavya.sotelo@warriorlife.net</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Gia</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ferraro</t>
+          <t>Sotelo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Financial Consulting (FCE)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2672,27 +2672,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ugo.lundgren@warriorlife.net</t>
+          <t>cyrus.dalmau@warriorlife.net</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ugo</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lundgren</t>
+          <t>Dalmau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2712,27 +2712,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mona.montague@warriorlife.net</t>
+          <t>mariam.mahmood@warriorlife.net</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Montague</t>
+          <t>Mahmood</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2752,27 +2752,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>devika.olivares@warriorlife.net</t>
+          <t>nasir.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Devika</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olivares</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2792,27 +2792,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yusuf.reyes@warriorlife.net</t>
+          <t>sinead.odhiambo@warriorlife.net</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Sinead</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>Odhiambo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2832,27 +2832,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Stellan Vargas</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>aurora.rugieroshanley@warriorlife.net</t>
+          <t>mirra.ravindran@warriorlife.net</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shanley</t>
+          <t>Ravindran</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2868,37 +2868,41 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sadie dahlberg</t>
+          <t>Kavya Sotelo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sadie.dahlberg@warriorlife.net</t>
+          <t>vivienne.zambrano@warriorlife.net</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sadie</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>dahlberg</t>
+          <t>Zambrano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Business Services Operations (BOR)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2913,32 +2917,28 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ainsley.pandit@warriorlife.net</t>
+          <t>sadie.dahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>sadie</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pandit</t>
+          <t>dahlberg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -2953,22 +2953,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>theo.sathe@warriorlife.net</t>
+          <t>neel.falconer@warriorlife.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sathe</t>
+          <t>Falconer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -2993,22 +2993,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>klara.serrano@warriorlife.net</t>
+          <t>ugo.lundgren@warriorlife.net</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Klara</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Serrano</t>
+          <t>Lundgren</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>peeira.souza@warriorlife.net</t>
+          <t>yusuf.reyes@warriorlife.net</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Quinn</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Reyes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3073,22 +3073,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ct.souza@warriorlife.net</t>
+          <t>tavish.rivas@warriorlife.net</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Vance Avani</t>
+          <t>Tavish</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Souza</t>
+          <t>Rivas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3113,22 +3113,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kasper.winterbourne@warriorlife.net</t>
+          <t>soren.rosales@warriorlife.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kasper</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Winterbourne</t>
+          <t>Rosales</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3153,22 +3153,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>t.zeidler@warriorlife.net</t>
+          <t>aurora.rugieroshanley@warriorlife.net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zeidler</t>
+          <t>Shanley</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+          <t>Finance Operations (FOR)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3184,34 +3184,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lila Granados</t>
+          <t>sadie dahlberg</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lila.granados@warriorlife.net</t>
+          <t>kasper.winterbourne@warriorlife.net</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lila</t>
+          <t>Kasper</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Granados</t>
+          <t>Winterbourne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -3229,32 +3233,28 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>valentina.achebe@warriorlife.net</t>
+          <t>lila.granados@warriorlife.net</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Lila</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>Granados</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Business Solutions Project (PMBS)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3269,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>zelda.demir@warriorlife.net</t>
+          <t>uma.madrigal@warriorlife.net</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Uma</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Demir</t>
+          <t>Madrigal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3309,17 +3309,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>tomas.gagnon@warriorlife.net</t>
+          <t>idris.mubarak@warriorlife.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3349,17 +3349,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>vera.kanellis@warriorlife.net</t>
+          <t>ceilialorcan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vera</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kanellis</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3389,17 +3389,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>lachlan.novak@warriorlife.net</t>
+          <t>nadia.whitlock@warriorlife.net</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Novak</t>
+          <t>Whitlock</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3429,22 +3429,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ivo.wanjiru@warriorlife.net</t>
+          <t>livia.yildirim@warriorlife.net</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ivo</t>
+          <t>Livia</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wanjiru</t>
+          <t>Yildirim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Business Solutions Project (PMBS)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3469,22 +3469,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>livia.yildirim@warriorlife.net</t>
+          <t>weilun.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Livia</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yildirim</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Business Solutions Project (PMBS)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3500,26 +3500,26 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Annika Jensen</t>
+          <t>Lila Granados</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>annika.jensen@warriorlife.net</t>
+          <t>kamal.sorensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Kamal</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>sorensen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3527,7 +3527,11 @@
           <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -3545,32 +3549,28 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>suri.escobar@warriorlife.net</t>
+          <t>annika.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Suri</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Escobar</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>esteban.haddad@warriorlife.net</t>
+          <t>davina.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Esteban</t>
+          <t>Davina</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Haddad</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3625,17 +3625,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>hassan.hollingsworth@warriorlife.net</t>
+          <t>felicity.avila@warriorlife.net</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Felicity</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hollingsworth</t>
+          <t>Avila</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3665,22 +3665,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>celine.wadsworth@warriorlife.net</t>
+          <t>oscar.draper@warriorlife.net</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Oscar</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wadsworth</t>
+          <t>Draper</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>aneesha.zabala@warriorlife.net</t>
+          <t>anders.havili@warriorlife.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Aneesha</t>
+          <t>Anders</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Zabala</t>
+          <t>Havili</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3745,17 +3745,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>dashiell.imogen@warriorlife.net</t>
+          <t>aria.ilyas@warriorlife.net</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>dashiell</t>
+          <t>Aria</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>imogen</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3776,37 +3776,41 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Annika Jensen</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>edda.krishnan@warriorlife.net</t>
+          <t>aidenbodhi.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Edda</t>
+          <t>Aiden-Bodhi</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Krishnan</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3816,37 +3820,33 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>v.eberhardt@warriorlife.net</t>
+          <t>tadeo.loureiro@warriorlife.net</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eberhardt</t>
+          <t>Loureiro</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Giving Project (PMCG)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -3856,27 +3856,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>naila.gagnon@warriorlife.net</t>
+          <t>valentina.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Naila</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gagnon</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3896,27 +3896,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>sienna.moreau@warriorlife.net</t>
+          <t>zelda.demir@warriorlife.net</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Demir</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -3936,27 +3936,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>fatima.redmond@warriorlife.net</t>
+          <t>salim.jarrah@warriorlife.net</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Salim</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redmond</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Community Giving Project (PMCG)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3976,27 +3976,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>colette.reinholt@warriorlife.net</t>
+          <t>vera.kanellis@warriorlife.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Colette</t>
+          <t>Vera</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Reinholt</t>
+          <t>Kanellis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4016,27 +4016,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>rhys.katayama@warriorlife.net</t>
+          <t>lachlan.novak@warriorlife.net</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>katayama</t>
+          <t>Novak</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4056,27 +4056,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Edda Krishnan</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>phebe.sifuentes@warriorlife.net</t>
+          <t>celine.wadsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Phoebe</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Wadsworth</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Business Growth Plan (EBG) *Must show legal proof of business ownership*</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4086,43 +4086,47 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tadeo Mercado</t>
+          <t>Tadeo Loureiro</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>tadeo.mercado@warriorlife.net</t>
+          <t>ivo.wanjiru@warriorlife.net</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Ivo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mercado</t>
+          <t>Wanjiru</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Community Awareness Project (PMCA)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4137,32 +4141,28 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>carmen.delacroix@warriorlife.net</t>
+          <t>tadeo.mercado@warriorlife.net</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Carmen</t>
+          <t>Tadeo</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Delacroix</t>
+          <t>Mercado</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Community Awareness Project (PMCA)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4177,22 +4177,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>eitan.lauridsen@warriorlife.net</t>
+          <t>linrui.bergstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Samara</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lauridsen</t>
+          <t>Bergstrom</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4217,22 +4217,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>olamide.noorani@warriorlife.net</t>
+          <t>an.doyle@warriorlife.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Noorani</t>
+          <t>Doyle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4257,22 +4257,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>cassian.nuri@warriorlife.net</t>
+          <t>suri.escobar@warriorlife.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cassian</t>
+          <t>Suri</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Escobar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4297,22 +4297,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>manon.nuri@warriorlife.net</t>
+          <t>esteban.haddad@warriorlife.net</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Manon Nuri</t>
+          <t>Esteban</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nuri</t>
+          <t>Haddad</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4337,22 +4337,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>d.brannordstrom@warriorlife.net</t>
+          <t>hassan.hollingsworth@warriorlife.net</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Hollingsworth</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4368,34 +4368,38 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>solene.moreau@warriorlife.net</t>
+          <t>wren.mikkelsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Solene</t>
+          <t>Wren</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Mikkelsen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -4404,31 +4408,31 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Solene Moreau</t>
+          <t>Tadeo Mercado</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>yael.caldeira@warriorlife.net</t>
+          <t>aneesha.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Yael</t>
+          <t>Aneesha</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Caldeira</t>
+          <t>Zabala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4438,7 +4442,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4453,17 +4457,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>kiran.chidozie@warriorlife.net</t>
+          <t>solene.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Solene</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chidozie</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4471,11 +4475,7 @@
           <t>Innovation Plan (EIP)</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -4493,17 +4493,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>lelerc.cisneros@warriorlife.net</t>
+          <t>yael.caldeira@warriorlife.net</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Yael</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cisneros</t>
+          <t>Caldeira</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4533,17 +4533,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>kwanming.maldonado@warriorlife.net</t>
+          <t>lelerc.cisneros@warriorlife.net</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sohan</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Maldonado</t>
+          <t>Cisneros</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4573,17 +4573,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>camila.mancini@warriorlife.net</t>
+          <t>kwanming.maldonado@warriorlife.net</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Sohan</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mancini</t>
+          <t>Maldonado</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>vikram.vaidya@warriorlife.net</t>
+          <t>fatima.redmond@warriorlife.net</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Vikram</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vaidya</t>
+          <t>Redmond</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4678,73 +4678,77 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>camila.obradovic@warriorlife.net</t>
+          <t>colette.reinholt@warriorlife.net</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Colette</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Obradovic</t>
+          <t>Reinholt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Camila Obradovic</t>
+          <t>Solene Moreau</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>renata.dhillon@warriorlife.net</t>
+          <t>dashiell.imogen@warriorlife.net</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>dashiell</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dhillon</t>
+          <t>imogen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4754,7 +4758,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4769,32 +4773,28 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>athena.dumont@warriorlife.net</t>
+          <t>camila.obradovic@warriorlife.net</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dumont</t>
+          <t>Obradovic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4809,22 +4809,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>corin.espinoza@warriorlife.net</t>
+          <t>kiran.chidozie@warriorlife.net</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Corin</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Espinoza</t>
+          <t>Chidozie</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4849,22 +4849,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sinead.gauthier@warriorlife.net</t>
+          <t>naila.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Naila</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gauthier</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -4889,17 +4889,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>maiam.jensen@warriorlife.net</t>
+          <t>camila.mancini@warriorlife.net</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Imogen Maeve</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jensen</t>
+          <t>Mancini</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>raina.melendez@warriorlife.net</t>
+          <t>sienna.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Raina</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Melendez</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -4969,22 +4969,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jarrah.ruggiero@warriorlife.net</t>
+          <t>vikram.vaidya@warriorlife.net</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Vikram</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ruggiero</t>
+          <t>Vaidya</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5000,34 +5000,38 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>darius.paredes@warriorlife.net</t>
+          <t>rhys.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>katayama</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Finance Operations (FOR)</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -5036,31 +5040,31 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Camila Obradovic</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>indira.andersen@warriorlife.net</t>
+          <t>phebe.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Indira</t>
+          <t>Phoebe</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>sifuentes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5070,7 +5074,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5080,37 +5084,33 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>gabriel.beaumont@warriorlife.net</t>
+          <t>ilana.palermo@warriorlife.net</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Ilana</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Beaumont</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Buying &amp; Merchandising Operations (BMOR)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>nalini.laghari@warriorlife.net</t>
+          <t>carmen.delacroix@warriorlife.net</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Nalini</t>
+          <t>Carmen</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Laghari</t>
+          <t>Delacroix</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>wren.mikkelsen@warriorlife.net</t>
+          <t>eitan.lauridsen@warriorlife.net</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wren</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mikkelsen</t>
+          <t>Lauridsen</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5200,27 +5200,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jian.moreau@warriorlife.net</t>
+          <t>olamide.noorani@warriorlife.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Moreau</t>
+          <t>Noorani</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5240,27 +5240,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ramona.nascimento@warriorlife.net</t>
+          <t>cassian.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ramona</t>
+          <t>Cassian</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -5280,27 +5280,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Darius Paredes</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>nils.vasquez@warriorlife.net</t>
+          <t>manon.nuri@warriorlife.net</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Nils</t>
+          <t>Manon Nuri</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vasquez</t>
+          <t>Nuri</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5316,37 +5316,41 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Ilana Palermo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>hina.sepulveda@warriorlife.net</t>
+          <t>d.brannordstrom@warriorlife.net</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Hina</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sepulveda</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+          <t>Independent Business Plan (EIB)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5356,37 +5360,33 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>kian.guerrero@warriorlife.net</t>
+          <t>darius.paredes@warriorlife.net</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Kian</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Finance Operations (FOR)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5396,27 +5396,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>lorcan.milburn@warriorlife.net</t>
+          <t>athena.dumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Lorcan</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Milburn</t>
+          <t>Dumont</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5436,27 +5436,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>senna.petrov@warriorlife.net</t>
+          <t>v.eberhardt@warriorlife.net</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Senna</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Petrov</t>
+          <t>Eberhardt</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -5476,22 +5476,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>alec.sheridan@warriorlife.net</t>
+          <t>sinead.gauthier@warriorlife.net</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Alec</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sheridan</t>
+          <t>Gauthier</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5516,27 +5516,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>zelda.tiwari@warriorlife.net</t>
+          <t>maiam.jensen@warriorlife.net</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Zelda</t>
+          <t>Imogen Maeve</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tiwari</t>
+          <t>Jensen</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5556,27 +5556,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Hina Sepulveda</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>lian.zoric@warriorlife.net</t>
+          <t>raina.melendez@warriorlife.net</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Lian</t>
+          <t>Raina</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zoric</t>
+          <t>Melendez</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Independent Business Plan (EIB)</t>
+          <t>Innovation Plan (EIP)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5592,34 +5592,38 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>nova.stanek@warriorlife.net</t>
+          <t>jarrah.ruggiero@warriorlife.net</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Nova</t>
+          <t>Jarrah</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stanek</t>
+          <t>Ruggiero</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr"/>
+          <t>Independent Business Plan (EIB)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -5628,31 +5632,31 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nova Stanek</t>
+          <t>Darius Paredes</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>linrui.bergstrom@warriorlife.net</t>
+          <t>zelda.tiwari@warriorlife.net</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Samara</t>
+          <t>Zelda</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bergstrom</t>
+          <t>Tiwari</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5677,32 +5681,28 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>an.doyle@warriorlife.net</t>
+          <t>nova.stanek@warriorlife.net</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Nova</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Doyle</t>
+          <t>Stanek</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5717,22 +5717,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>nara.garrido@warriorlife.net</t>
+          <t>tomas.gagnon@warriorlife.net</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Nara</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Gagnon</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5757,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>tuan.hartley@warriorlife.net</t>
+          <t>nara.garrido@warriorlife.net</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Nara</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hartley</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5797,22 +5797,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>theo.herrera@warriorlife.net</t>
+          <t>tuan.hartley@warriorlife.net</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Hartley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -5837,22 +5837,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>harlow.savage@warriorlife.net</t>
+          <t>theo.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Harlow</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Savage</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5877,22 +5877,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>manus.sifuentes@warriorlife.net</t>
+          <t>eamon.kasprzak@warriorlife.net</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Imani</t>
+          <t>Eamon</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sifuentes</t>
+          <t>Kasprzak</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
+          <t>Franchise Business Plan (EFB)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5902,40 +5902,44 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>astrid.kaufman@warriorlife.net</t>
+          <t>harlow.savage@warriorlife.net</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>astrid</t>
+          <t>Harlow</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>kaufman</t>
+          <t>Savage</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>International Business Plan (IBP)</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -5944,31 +5948,31 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Nova Stanek</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>eamon.kasprzak@warriorlife.net</t>
+          <t>manus.sifuentes@warriorlife.net</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Eamon</t>
+          <t>Imani</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kasprzak</t>
+          <t>Sifuentes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5978,7 +5982,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -5988,37 +5992,33 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>uma.madrigal@warriorlife.net</t>
+          <t>hazel.svensson@warriorlife.net</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Uma</t>
+          <t>Hazel</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Madrigal</t>
+          <t>Svensson</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Innovation Plan (EIP)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6028,27 +6028,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>idris.mubarak@warriorlife.net</t>
+          <t>indira.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Indira</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6068,27 +6068,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ceilialorcan.vargas@warriorlife.net</t>
+          <t>gabriel.beaumont@warriorlife.net</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Beaumont</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -6108,27 +6108,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>nadia.whitlock@warriorlife.net</t>
+          <t>renata.dhillon@warriorlife.net</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Whitlock</t>
+          <t>Dhillon</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>International Business Plan (IBP)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6148,27 +6148,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>weilun.sifuentes@warriorlife.net</t>
+          <t>nalini.laghari@warriorlife.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Nalini</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>sifuentes</t>
+          <t>Laghari</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6188,27 +6188,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>astrid kaufman</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>kamal.sorensen@warriorlife.net</t>
+          <t>jian.moreau@warriorlife.net</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Kamal</t>
+          <t>Jian</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>sorensen</t>
+          <t>Moreau</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6218,68 +6218,72 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>meilan.zabala@warriorlife.net</t>
+          <t>ramona.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>delphine</t>
+          <t>Ramona</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>zabala</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Franchise Business Plan (EFB)</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>Start-Up Business Plan (ESB)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>Hazel Svensson</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>davina.avila@warriorlife.net</t>
+          <t>nils.vasquez@warriorlife.net</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Davina</t>
+          <t>Nils</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Vasquez</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6304,37 +6308,33 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>felicity.avila@warriorlife.net</t>
+          <t>astrid.kaufman@warriorlife.net</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Felicity</t>
+          <t>astrid</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>kaufman</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>International Business Plan (IBP)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6344,27 +6344,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>oscar.draper@warriorlife.net</t>
+          <t>corin.espinoza@warriorlife.net</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Oscar</t>
+          <t>Corin</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Draper</t>
+          <t>Espinoza</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6384,27 +6384,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>anders.havili@warriorlife.net</t>
+          <t>kian.guerrero@warriorlife.net</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Anders</t>
+          <t>Kian</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Havili</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6424,27 +6424,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>aria.ilyas@warriorlife.net</t>
+          <t>lorcan.milburn@warriorlife.net</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Aria</t>
+          <t>Lorcan</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Milburn</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6464,27 +6464,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>delphine zabala</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>aidenbodhi.vargas@warriorlife.net</t>
+          <t>senna.petrov@warriorlife.net</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Aiden-Bodhi</t>
+          <t>Senna</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vargas</t>
+          <t>Petrov</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6500,34 +6500,38 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>tadeo.loureiro@warriorlife.net</t>
+          <t>alec.sheridan@warriorlife.net</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Tadeo</t>
+          <t>Alec</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Loureiro</t>
+          <t>Sheridan</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr"/>
+          <t>Independent Business Plan (EIB)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H155" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -6536,31 +6540,31 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>astrid kaufman</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>sk.alvarez@warriorlife.net</t>
+          <t>lian.zoric@warriorlife.net</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Lian</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Alvarez</t>
+          <t>Zoric</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Independent Business Plan (EIB)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6580,34 +6584,30 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>shai.darrow@warriorlife.net</t>
+          <t>edda.krishnan@warriorlife.net</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Shai</t>
+          <t>Edda</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Darrow</t>
+          <t>Krishnan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Professional Selling (HTPS)</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -6620,27 +6620,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>kenji.herrera@warriorlife.net</t>
+          <t>tarek.adeyemi@warriorlife.net</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Kenji</t>
+          <t>Tarek</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6660,27 +6660,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>salim.jarrah@warriorlife.net</t>
+          <t>svea.brandt@warriorlife.net</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Salim</t>
+          <t>Svea</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Jarrah</t>
+          <t>Brandt</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Community Giving Project (PMCG)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6700,27 +6700,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>lyra.katayama@warriorlife.net</t>
+          <t>diya.fitzgerald@warriorlife.net</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Lyra</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Katayama</t>
+          <t>Fitzgerald</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -6740,27 +6740,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tadeo Loureiro</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>anton.mbeki@warriorlife.net</t>
+          <t>chandra.fonseca@warriorlife.net</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Chandra</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Mbeki</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6776,62 +6776,66 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ilana.palermo@warriorlife.net</t>
+          <t>elara.mehrotra@warriorlife.net</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Ilana</t>
+          <t>Elara</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mehrotra</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Buying &amp; Merchandising Operations (BMOR)</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Edda Krishnan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>tarek.adeyemi@warriorlife.net</t>
+          <t>ayaan.villanueva@warriorlife.net</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Tarek</t>
+          <t>Ayaan</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Villanueva</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6856,37 +6860,33 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>malia.andersen@warriorlife.net</t>
+          <t>stellan.vargas@warriorlife.net</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Malia</t>
+          <t>Stellan</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Andersen</t>
+          <t>Vargas</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Hospitality &amp; Tourism Operations (HTOR)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -6896,27 +6896,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>svea.brandt@warriorlife.net</t>
+          <t>yara.gundersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Svea</t>
+          <t>Yara</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Brandt</t>
+          <t>Gundersen</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6936,27 +6936,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>chiara.callahan@warriorlife.net</t>
+          <t>anton.mbeki@warriorlife.net</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Chiara</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Callahan</t>
+          <t>Mbeki</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6976,27 +6976,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>chandra.fonseca@warriorlife.net</t>
+          <t>emeka.nascimento@warriorlife.net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Chandra</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Fonseca</t>
+          <t>Nascimento</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7016,27 +7016,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>elara.mehrotra@warriorlife.net</t>
+          <t>eero.rothman@warriorlife.net</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Elara</t>
+          <t>Eero</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Mehrotra</t>
+          <t>Rothman</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7056,27 +7056,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ilana Palermo</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ayaan.villanueva@warriorlife.net</t>
+          <t>kavya.wahlberg@warriorlife.net</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Villanueva</t>
+          <t>Wahlberg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Service (IMCS)</t>
+          <t>Business Services Operations (BOR)</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7092,37 +7092,41 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>Stellan Vargas</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>hazel.svensson@warriorlife.net</t>
+          <t>ameer.bosco@warriorlife.net</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Hazel</t>
+          <t>ameer</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Svensson</t>
+          <t>bosco</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Innovation Plan (EIP)</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7132,37 +7136,33 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>diya.fitzgerald@warriorlife.net</t>
+          <t>meilan.zabala@warriorlife.net</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>delphine</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Fitzgerald</t>
+          <t>zabala</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+          <t>Franchise Business Plan (EFB)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7172,27 +7172,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>marco.greenway@warriorlife.net</t>
+          <t>sk.alvarez@warriorlife.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Greenway</t>
+          <t>Alvarez</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Experienced</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -7212,27 +7212,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>emeka.nascimento@warriorlife.net</t>
+          <t>malia.andersen@warriorlife.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Malia</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Nascimento</t>
+          <t>Andersen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7252,27 +7252,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>tavish.rivas@warriorlife.net</t>
+          <t>chiara.callahan@warriorlife.net</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Tavish</t>
+          <t>Chiara</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rivas</t>
+          <t>Callahan</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Service (IMCS)</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7292,27 +7292,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>eero.rothman@warriorlife.net</t>
+          <t>shai.darrow@warriorlife.net</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Eero</t>
+          <t>Shai</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Rothman</t>
+          <t>Darrow</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7332,27 +7332,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Hazel Svensson</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ashwin.trevino@warriorlife.net</t>
+          <t>kenji.herrera@warriorlife.net</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Ashwin</t>
+          <t>Kenji</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Trevino</t>
+          <t>Herrera</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7362,40 +7362,44 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>siri zhelezny</t>
+          <t>delphine zabala</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>siri.zhelezny@warriorlife.net</t>
+          <t>lyra.katayama@warriorlife.net</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>siri</t>
+          <t>Lyra</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>zhelezny</t>
+          <t>Katayama</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr"/>
+          <t>Integrated Marketing Campaign - Event (IMCE)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Compete</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr">
         <is>
           <t>Experienced</t>
@@ -7413,17 +7417,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>gemma.achebe@warriorlife.net</t>
+          <t>siri.zhelezny@warriorlife.net</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>siri</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Achebe</t>
+          <t>zhelezny</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7431,14 +7435,10 @@
           <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Compete</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Novice</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
@@ -7453,22 +7453,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>s.bakke@warriorlife.net</t>
+          <t>gemma.achebe@warriorlife.net</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Bakke</t>
+          <t>Achebe</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Start-Up Business Plan (ESB)</t>
+          <t>Integrated Marketing Campaign - Product (IMCP)</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7493,22 +7493,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>yara.gundersen@warriorlife.net</t>
+          <t>s.bakke@warriorlife.net</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Yara</t>
+          <t>Kabir</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Gundersen</t>
+          <t>Bakke</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Integrated Marketing Campaign - Product (IMCP)</t>
+          <t>Start-Up Business Plan (ESB)</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7653,17 +7653,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ameer.bosco@warriorlife.net</t>
+          <t>ashwin.trevino@warriorlife.net</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>ameer</t>
+          <t>Ashwin</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>bosco</t>
+          <t>Trevino</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
